--- a/SCOSy Alignment.xlsx
+++ b/SCOSy Alignment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/SCO-to-COSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F50554-358D-D64D-89A5-C910C0898CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC888F25-5804-3C4B-8AC7-BE736063631B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7600" yWindow="500" windowWidth="19340" windowHeight="16520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="121">
   <si>
     <t>Equivalence between the two classes</t>
   </si>
@@ -430,7 +430,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,6 +515,24 @@
         <bgColor rgb="FFEAD1DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0C8D4"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0C8D4"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -543,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -568,7 +586,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -581,6 +598,10 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1481,32 +1502,34 @@
       <c r="H27" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="I27" s="24"/>
+      <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="14" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="G28" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="36"/>
     </row>
     <row r="29" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
@@ -1565,29 +1588,29 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" ht="14" x14ac:dyDescent="0.2">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="22" t="s">
@@ -1611,7 +1634,7 @@
       <c r="G32" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="26" t="s">
         <v>37</v>
       </c>
       <c r="I32" s="22"/>
@@ -1663,54 +1686,54 @@
       <c r="I34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="14" x14ac:dyDescent="0.2">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:10" ht="14" x14ac:dyDescent="0.2">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F36" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G36" s="26" t="s">
+      <c r="G36" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="22" t="s">
@@ -1734,7 +1757,7 @@
       <c r="G37" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="H37" s="27" t="s">
+      <c r="H37" s="26" t="s">
         <v>37</v>
       </c>
       <c r="I37" s="22"/>
@@ -1782,7 +1805,7 @@
       <c r="G39" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="H39" s="27" t="s">
+      <c r="H39" s="26" t="s">
         <v>37</v>
       </c>
       <c r="I39" s="22"/>
@@ -1809,10 +1832,10 @@
       <c r="G40" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="27" t="s">
+      <c r="H40" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="I40" s="27"/>
+      <c r="I40" s="26"/>
     </row>
     <row r="41" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
@@ -1886,7 +1909,7 @@
       <c r="G43" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="H43" s="27" t="s">
+      <c r="H43" s="26" t="s">
         <v>85</v>
       </c>
       <c r="I43" s="22"/>
@@ -1917,31 +1940,31 @@
       <c r="I44" s="22"/>
     </row>
     <row r="45" spans="1:10" ht="14" x14ac:dyDescent="0.2">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="E45" s="28" t="s">
+      <c r="E45" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="G45" s="30" t="s">
+      <c r="G45" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="H45" s="31" t="s">
+      <c r="H45" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="I45" s="28"/>
+      <c r="I45" s="27"/>
     </row>
     <row r="46" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="16" t="s">
@@ -1968,31 +1991,31 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="14" x14ac:dyDescent="0.2">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="C47" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="F47" s="32" t="s">
+      <c r="F47" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="G47" s="33" t="s">
+      <c r="G47" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H47" s="32" t="s">
+      <c r="H47" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="I47" s="32"/>
+      <c r="I47" s="31"/>
     </row>
     <row r="48" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="16" t="s">
@@ -2290,27 +2313,27 @@
       <c r="I60" s="18"/>
     </row>
     <row r="61" spans="1:9" ht="14" x14ac:dyDescent="0.2">
-      <c r="A61" s="34" t="s">
+      <c r="A61" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="35" t="s">
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="H61" s="36" t="s">
+      <c r="H61" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="I61" s="34"/>
+      <c r="I61" s="33"/>
     </row>
     <row r="62" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">

--- a/SCOSy Alignment.xlsx
+++ b/SCOSy Alignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/SCO-to-COSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6360B9BB-8011-ED4E-A785-1FFD3FBF2950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE9C5A5-294A-D146-9141-19007F1766B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legenda" sheetId="1" r:id="rId1"/>
@@ -21,16 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="146">
-  <si>
-    <t>Equivalence between the two classes</t>
-  </si>
-  <si>
-    <t>Subclass of</t>
-  </si>
-  <si>
-    <t>no corresponding class</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="154">
   <si>
     <t>overlapping</t>
   </si>
@@ -203,9 +194,6 @@
     <t>disposition to participate in an interaction</t>
   </si>
   <si>
-    <t>disposition to act can also charactize a system enviroment component in SCO, but in COSy component disposition just characterizes component (there is an Overlapping).  We can add patterns to the ontologies to specify this Overlapping, such as creating specific Subclasses in SCO, or more general/external entitty-focused classes.</t>
-  </si>
-  <si>
     <t>disposition to act</t>
   </si>
   <si>
@@ -422,9 +410,6 @@
     <t>SCO “interaction” class refers to events where participants have a causative effect on one another. It is a complete class with respect to interactions involving system and system environment components. Disc-O “interaction” class presents the same coverage, without being a complete class with respect to component interaction. Thus, the first is a subclass of the latter. COSy includes a subclass for interactions among system components (ComponentInternalInteraction) and a subclass between system component and external entity (ComponentExternalInteraction). Those classes are equivalent to the two SCO “interaction” subclasses “interaction among system components” and “interaction between system components and system environment component”. Instead, no further mapping over that the subsumption subsists for the SCO “interaction among system environment components” as COSy does not cover a specific class for these interactions.</t>
   </si>
   <si>
-    <t>The focus is on aspects of systems, whatever the systems are. So, we can map directly these classes without dealing with the fact that SCO and COSy diverge over functional roles of compoents.</t>
-  </si>
-  <si>
     <t>The SCO class “complex system property is meant as a grouping class for properties concerning complex systems. Thus, it can be mapped as a subclass of COSy “SystemAspect” that refers generally to aspects inheriting in systems. Related subclasses follow the mapping as subclass.</t>
   </si>
   <si>
@@ -434,31 +419,70 @@
     <t>Mapped through a new class</t>
   </si>
   <si>
-    <t>Indirectly mapped though mapping upper-level classes.</t>
-  </si>
-  <si>
     <t>The focus is on history of systems, whatever the systems are. So, we can map these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
   </si>
   <si>
     <t>The focus is on system interactions, whatever the systems are. So, we can map  these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
   </si>
   <si>
-    <t>Mapped through a new class.</t>
-  </si>
-  <si>
     <t>Indirectly mapped through mapping upper-level classes. The focus is on system interactions, whatever the systems are. So, we can map  these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
   </si>
   <si>
-    <t>Indirectly mapped through mapping upper-level classes. The focus is on systems situations, whatever the systems are. So, we can map these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
-  </si>
-  <si>
     <t>The focus is on systems situations, whatever the systems are. So, we can map these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
   </si>
   <si>
-    <t>Indirectly mapped though mapping super-level class.</t>
-  </si>
-  <si>
     <t>The SCO “perspective” class refers to dispositions that inherits in complex system components and related environment components. This class coverage overlaps with that of the COSy “ComponentDisposition” class with respect to the perspectives of complex system components because the COSy class refers to all possible dispositions of system components. We created an ad hoc class for perspectives of system components. It is a subclass of both the SCO “perspective” class and COSy “ComponentDisposition” and instantiates the gUFO “subkind” class.</t>
+  </si>
+  <si>
+    <t>We followed the same approach presented for the SCO “perspective” class, n mapping the SCO “disposition to participate in an interaction” and its subclass” disposition to act” to the COSy “ComponentDisposition” class. This is because these classes refer to both system components and system environment components. We created specific classes for dispositions of a system component to participate in an interaction and dispositions to act of a system component. Please, refer to the perspective mapping, adjusting subsumption and instantiation to adequate gUFO classes.</t>
+  </si>
+  <si>
+    <t>Both SCO and COSy interpret systems with respect to related components. Nevertheless, SCO adopts a generalist and neutral approach where a system is as such independently from the functions and roles played by its components, while COSy requires this grounding. The two ontologies also diverge in terms of type instantiation; the first sees system as a gUFO sortal while the second sees it as a gUFO non-sortal. We created an ad hoc class for functional systems (systems where components play different functional roles). It is a subclass of both the SCO “system” class and COSy “system” and instantiates the gUFO “role” class and COSy “system type” classes. The same approach has been applied to the SCO “system component” class and COSy “Component”, creating an ad hoc class for functional system components (components that are part of a functional system and play different functional roles). Subclass mapping has been addressed in the same manner in both cases, adjusting subsumption and instantiation to adequate gUFO classes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCO treats system environment components in the same manner as system components, but with respect to system environments. COSy, instead, interprets external entities as objects outside the system that interact with the system at a given moment. Thus, we mapped the COSY “externalEntity” class as a subclass of SCO “system environment component” and created an ad hoc class for complex system environment components following the COSY approach. Further subclasses are indirectly mapped through these upper-level classes.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SCO treats system environment components in the same manner as system components, but with respect to system environments. COSy, instead, interprets external entities as objects outside the system that interact with the system at a given moment. Thus, we mapped the COSY “externalEntity” class as a subclass of SCO “system environment component” and created an ad hoc class for complex system environment components following the COSY approach. Further subclasses are indirectly mapped through these upper-level classes.	</t>
+  </si>
+  <si>
+    <t>Both SCO and COSy interpret systems with respect to related components. Nevertheless, SCO adopts a generalist and neutral approach where a system is as such independently from the functions and roles played by its components, while COSy requires this grounding. The two ontologies also diverge in terms of type instantiation; the first sees system as a gUFO sortal while the second sees it as a gUFO non-sortal. We created an ad hoc class for functional systems (systems where components play different functional roles). It is a subclass of both the SCO “system” class and COSy “system” and instantiates the gUFO “role” class and COSy “system type” classes. The same approach has been applied to the SCO “system component” class and COSy “Component”, creating an ad hoc class for functional system components (components that are part of a functional system and play different functional roles). Subclass mapping has been addressed in the same manner in both cases, adjusting subsumption and instantiation to adequate gUFO classes.Further subclasses are indirectly mapped through these upper-level classes.</t>
+  </si>
+  <si>
+    <t>Both SCO and COSy interpret systems with respect to related components. Nevertheless, SCO adopts a generalist and neutral approach where a system is as such independently from the functions and roles played by its components, while COSy requires this grounding. The two ontologies also diverge in terms of type instantiation; the first sees system as a gUFO sortal while the second sees it as a gUFO non-sortal. We created an ad hoc class for functional systems (systems where components play different functional roles). It is a subclass of both the SCO “system” class and COSy “system” and instantiates the gUFO “role” class and COSy “system type” classes. The same approach has been applied to the SCO “system component” class and COSy “Component”, creating an ad hoc class for functional system components (components that are part of a functional system and play different functional roles). Subclass mapping has been addressed in the same manner in both cases, adjusting subsumption and instantiation to adequate gUFO classes. Further subclasses are indirectly mapped through these upper-level classes.</t>
+  </si>
+  <si>
+    <t>Indirectly mapped through mapping upper-level classes.</t>
+  </si>
+  <si>
+    <t>Indirectly mapped throughmapping upper-level classes.</t>
+  </si>
+  <si>
+    <t>The focus is on aspects of systems, whatever the systems are. So, we can map  these classes without dealing with the fact that SCO and COSy diverge over functional roles of compoents.</t>
+  </si>
+  <si>
+    <t>The focus is on aspects of systems, whatever the systems are. So, we can map these classes without dealing with the fact that SCO and COSy diverge over functional roles of compoents.</t>
+  </si>
+  <si>
+    <t>Mapped througha new class.</t>
+  </si>
+  <si>
+    <t>Indirectly mapped trhough mapping upper-level classes. The focus is on system interactions, whatever the systems are. So, we can map  these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
+  </si>
+  <si>
+    <t>Indirectly mapped trhough mapping upper-level classes. The focus is on systems situations, whatever the systems are. So, we can map these classes without dealing with the fact that SCO and COSy diverge over functional roles of components.</t>
+  </si>
+  <si>
+    <t>Indirectly mapped through mapping super-level class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivalence </t>
+  </si>
+  <si>
+    <t>Subsumption</t>
+  </si>
+  <si>
+    <t>no correspondence</t>
   </si>
 </sst>
 </file>
@@ -505,7 +529,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,12 +646,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF02FF00"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
@@ -660,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -691,10 +709,9 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -928,37 +945,37 @@
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5"/>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -981,1917 +998,1948 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
       <c r="E3" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="F9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="G9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="H9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="I9" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J9" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="I10" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J10" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J11" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J12" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J13" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J14" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
       <c r="H15" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="J19" s="16" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J20" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="15"/>
+        <v>144</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>54</v>
-      </c>
       <c r="I25" s="17" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J25" s="27" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="J26" s="27" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>26</v>
-      </c>
       <c r="H27" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D28" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="H28" s="26" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D29" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>26</v>
-      </c>
       <c r="H29" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="K29" s="30"/>
+        <v>137</v>
+      </c>
+      <c r="K29" s="31"/>
     </row>
     <row r="30" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="30"/>
+        <v>147</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K30" s="31"/>
     </row>
     <row r="31" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>138</v>
+        <v>60</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>132</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="K33" s="32"/>
+        <v>127</v>
+      </c>
+      <c r="K33" s="31"/>
     </row>
     <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I34" s="29"/>
       <c r="J34" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="K34" s="32"/>
+        <v>128</v>
+      </c>
+      <c r="K34" s="31"/>
     </row>
     <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="33" t="s">
-        <v>139</v>
+        <v>60</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>133</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="32"/>
+        <v>128</v>
+      </c>
+      <c r="K35" s="31"/>
     </row>
     <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="33" t="s">
-        <v>139</v>
+        <v>60</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>133</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="K36" s="32"/>
+        <v>128</v>
+      </c>
+      <c r="K36" s="31"/>
     </row>
     <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J40" s="28" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>14</v>
+        <v>73</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>11</v>
       </c>
       <c r="I41" s="29"/>
       <c r="J41" s="29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="K44" s="32"/>
+        <v>119</v>
+      </c>
+      <c r="K44" s="31"/>
     </row>
     <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="K45" s="32"/>
+        <v>123</v>
+      </c>
+      <c r="K45" s="31"/>
     </row>
     <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="14"/>
       <c r="G46" s="14"/>
       <c r="H46" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="K46" s="32" t="s">
-        <v>113</v>
+        <v>124</v>
+      </c>
+      <c r="K46" s="31" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="K47" s="32"/>
+        <v>123</v>
+      </c>
+      <c r="K47" s="31"/>
     </row>
     <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="K48" s="32"/>
+        <v>124</v>
+      </c>
+      <c r="K48" s="31"/>
     </row>
     <row r="49" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I49" s="14"/>
-      <c r="J49" s="31" t="s">
-        <v>125</v>
+      <c r="J49" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I52" s="14"/>
-      <c r="J52" s="31" t="s">
-        <v>125</v>
+      <c r="J52" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I53" s="14"/>
       <c r="J53" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
       <c r="H54" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I54" s="14"/>
       <c r="J54" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A55" s="14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
       <c r="H55" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I57" s="14"/>
-      <c r="J57" s="31" t="s">
-        <v>125</v>
+      <c r="J57" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I58" s="14"/>
       <c r="J58" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="K58" s="31"/>
     </row>
     <row r="59" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
       <c r="H59" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
-        <v>125</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="K59" s="31"/>
     </row>
     <row r="60" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J60" s="15"/>
-      <c r="K60" s="30"/>
+        <v>143</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K60" s="31"/>
     </row>
     <row r="61" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
       <c r="H61" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J61" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="K61" s="32"/>
+        <v>136</v>
+      </c>
+      <c r="K61" s="31"/>
     </row>
     <row r="62" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I62" s="14"/>
-      <c r="J62" s="31" t="s">
-        <v>125</v>
-      </c>
+      <c r="J62" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K62" s="31"/>
     </row>
     <row r="63" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="K63" s="31"/>
     </row>
     <row r="64" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F64" s="14"/>
       <c r="G64" s="14"/>
       <c r="H64" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I64" s="14"/>
       <c r="J64" s="14" t="s">
-        <v>119</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="K64" s="31"/>
     </row>
     <row r="65" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G65" s="15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="J65" s="15"/>
-      <c r="K65" s="30"/>
+        <v>143</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K65" s="31"/>
     </row>
     <row r="66" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A66" s="14" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="14"/>
       <c r="H66" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I66" s="14"/>
       <c r="J66" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="K66" s="32"/>
+        <v>122</v>
+      </c>
+      <c r="K66" s="31"/>
     </row>
     <row r="67" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="14"/>
       <c r="H67" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I67" s="14"/>
-      <c r="J67" s="31" t="s">
-        <v>125</v>
+      <c r="J67" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="14" x14ac:dyDescent="0.2">
